--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -397,28 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S3"/>
-  <cols>
-    <col min="1" max="1" width="35.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-    <col min="9" max="9" width="30.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="15.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
-    <col min="15" max="15" width="8.83203125" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="17" width="10.83203125" customWidth="1"/>
-    <col min="18" max="18" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="40.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:S7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -532,10 +511,10 @@
         <v>30</v>
       </c>
       <c r="R2" t="str">
-        <v>SUCCESS</v>
+        <v>FAILED</v>
       </c>
       <c r="S2" t="str">
-        <v>orion@detroitautomotive.onmicrosoft.com</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -597,9 +576,245 @@
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>quill.sterling@stlouisresearch.us</v>
+      </c>
+      <c r="B4" t="str">
+        <v>BioQuill8901@StLouis</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Quill</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Sterling</v>
+      </c>
+      <c r="E4" t="str">
+        <v>St Louis Research Institute</v>
+      </c>
+      <c r="F4" t="str">
+        <v>1 person</v>
+      </c>
+      <c r="G4" t="str">
+        <v>+13145558901</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Biomedical Researcher</v>
+      </c>
+      <c r="I4" t="str">
+        <v>4444 Forest Park Avenue</v>
+      </c>
+      <c r="J4" t="str">
+        <v>St Louis</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Missouri</v>
+      </c>
+      <c r="L4" t="str">
+        <v>63108</v>
+      </c>
+      <c r="M4" t="str">
+        <v>United States</v>
+      </c>
+      <c r="N4" t="str">
+        <v>5198939816602718</v>
+      </c>
+      <c r="O4" t="str">
+        <v>213</v>
+      </c>
+      <c r="P4" t="str">
+        <v>03</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>30</v>
+      </c>
+      <c r="R4" t="str">
+        <v>FAILED</v>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>raven.black@baltimoremarine.us</v>
+      </c>
+      <c r="B5" t="str">
+        <v>MarineRaven6789@Baltimore</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Raven</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Black</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Baltimore Marine Institute</v>
+      </c>
+      <c r="F5" t="str">
+        <v>1 person</v>
+      </c>
+      <c r="G5" t="str">
+        <v>+14105556789</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Marine Biologist</v>
+      </c>
+      <c r="I5" t="str">
+        <v>601 East Pratt Street</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Baltimore</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Maryland</v>
+      </c>
+      <c r="L5" t="str">
+        <v>21202</v>
+      </c>
+      <c r="M5" t="str">
+        <v>United States</v>
+      </c>
+      <c r="N5" t="str">
+        <v>5198939816602718</v>
+      </c>
+      <c r="O5" t="str">
+        <v>213</v>
+      </c>
+      <c r="P5" t="str">
+        <v>03</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>30</v>
+      </c>
+      <c r="R5" t="str">
+        <v>FAILED</v>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>sylvan.reed@phoenixsolar.us</v>
+      </c>
+      <c r="B6" t="str">
+        <v>SolarSylvan1234@Phoenix</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Sylvan</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Reed</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Phoenix Solar Energy</v>
+      </c>
+      <c r="F6" t="str">
+        <v>1 person</v>
+      </c>
+      <c r="G6" t="str">
+        <v>+16025551234</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Solar Engineer</v>
+      </c>
+      <c r="I6" t="str">
+        <v>234 North Central Avenue</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Phoenix</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Arizona</v>
+      </c>
+      <c r="L6" t="str">
+        <v>85004</v>
+      </c>
+      <c r="M6" t="str">
+        <v>United States</v>
+      </c>
+      <c r="N6" t="str">
+        <v>5198939816602718</v>
+      </c>
+      <c r="O6" t="str">
+        <v>213</v>
+      </c>
+      <c r="P6" t="str">
+        <v>03</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>30</v>
+      </c>
+      <c r="R6" t="str">
+        <v>FAILED</v>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>thorne.wilder@nashvillemusic.us</v>
+      </c>
+      <c r="B7" t="str">
+        <v>MusicThorne8901@Nashville</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Thorne</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Wilder</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Nashville Music Group</v>
+      </c>
+      <c r="F7" t="str">
+        <v>1 person</v>
+      </c>
+      <c r="G7" t="str">
+        <v>+16155558901</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Music Producer</v>
+      </c>
+      <c r="I7" t="str">
+        <v>222 5th Avenue South</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Nashville</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Tennessee</v>
+      </c>
+      <c r="L7" t="str">
+        <v>37203</v>
+      </c>
+      <c r="M7" t="str">
+        <v>United States</v>
+      </c>
+      <c r="N7" t="str">
+        <v>5198939816602718</v>
+      </c>
+      <c r="O7" t="str">
+        <v>213</v>
+      </c>
+      <c r="P7" t="str">
+        <v>03</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>30</v>
+      </c>
+      <c r="R7" t="str">
+        <v>FAILED</v>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S7"/>
   </ignoredErrors>
 </worksheet>
 </file>